--- a/artfynd/A 30034-2024 artfynd.xlsx
+++ b/artfynd/A 30034-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94391984</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405085.8542199959</v>
+        <v>405086</v>
       </c>
       <c r="R2" t="n">
-        <v>7014442.548545734</v>
+        <v>7014442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94391981</v>
+        <v>94391978</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,34 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405047.9166646641</v>
+        <v>405070</v>
       </c>
       <c r="R3" t="n">
-        <v>7014533.827417565</v>
+        <v>7014712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,43 +858,34 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,44 +896,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Staaf, Felicia Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94391982</v>
+        <v>94391989</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405080.0569011545</v>
+        <v>405094</v>
       </c>
       <c r="R4" t="n">
-        <v>7014429.645856491</v>
+        <v>7014444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,21 +971,11 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,6 +984,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,50 +1015,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94391989</v>
+        <v>94391977</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405094.0126459887</v>
+        <v>405070</v>
       </c>
       <c r="R5" t="n">
-        <v>7014443.660590569</v>
+        <v>7014712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,27 +1086,18 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1161,60 +1124,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Staaf, Felicia Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94391978</v>
+        <v>94391982</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405069.4235459233</v>
+        <v>405080</v>
       </c>
       <c r="R6" t="n">
-        <v>7014712.155168594</v>
+        <v>7014429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,45 +1199,19 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1292,22 +1221,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Staaf, Felicia Olsson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94391977</v>
+        <v>79456894</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,37 +1239,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Betespräglad skog vid Ytterstvallen, Jmt</t>
+          <t>Leden till Yttertstvallen, Ytterstvallen, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405069.4235459233</v>
+        <v>404914</v>
       </c>
       <c r="R7" t="n">
-        <v>7014712.155168594</v>
+        <v>7014713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,22 +1305,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,33 +1323,131 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf, Felicia Olsson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131293507</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ytterstvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>405087</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7015233</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>9ee5b947-4811-4b49-a667-44170e8e2b17</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30034-2024 artfynd.xlsx
+++ b/artfynd/A 30034-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391984</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391989</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134881566</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134881567</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94391982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79456894</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,8 +1707,24 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>